--- a/Kitap1.xlsx
+++ b/Kitap1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huseyinsinik/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B40DCB9D-82EA-8644-AF23-E087961DF708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8BEAE8-A9CA-A241-9619-517BC22F779C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5080" yWindow="1860" windowWidth="28240" windowHeight="17240" xr2:uid="{4017CBC8-9DC9-6845-B2E6-E9FB5B2A810F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="286">
   <si>
     <t>Kültür</t>
   </si>
@@ -441,24 +441,469 @@
   </si>
   <si>
     <t>İlk sivil havacılık okulu Vecihi Hürkuş tarafından kurulmuştur.</t>
+  </si>
+  <si>
+    <t>Osmanlı Devleti'nde ilk gümüş akçe Orhan Bey döneminde basılmıştır.</t>
+  </si>
+  <si>
+    <t>Rumeli Hisarı, Fatih Sultan Mehmet tarafından yaptırılmıştır.</t>
+  </si>
+  <si>
+    <t>Osmanlı'da ilk çiçek aşısı Lale Devri'nde uygulanmıştır.</t>
+  </si>
+  <si>
+    <t>Sened-i İttifak, II. Mahmut ile Ayanlar arasında imzalanmıştır.</t>
+  </si>
+  <si>
+    <t>Tanzimat Fermanı 1839 yılında Abdülmecit döneminde ilan edilmiştir.</t>
+  </si>
+  <si>
+    <t>Islahat Fermanı 1856 yılında gayrimüslimlere haklar tanımak için ilan edilmiştir.</t>
+  </si>
+  <si>
+    <t>Osmanlı'da ilk anayasa olan Kanun-i Esasi 1876'da yürürlüğe girmiştir.</t>
+  </si>
+  <si>
+    <t>Duyun-u Umumiye İdaresi, Osmanlı'nın dış borçlarını denetlemek için kurulmuştur.</t>
+  </si>
+  <si>
+    <t>Trablusgarp Savaşı, Mustafa Kemal'in emperyalizme karşı ilk savaşıdır.</t>
+  </si>
+  <si>
+    <t>İnkılap Tarihi</t>
+  </si>
+  <si>
+    <t>I. Balkan Savaşı sonucunda Osmanlı Devleti Midye-Enez hattının doğusuna çekilmiştir.</t>
+  </si>
+  <si>
+    <t>Mondros Ateşkes Antlaşması 30 Ekim 1918'de imzalanmıştır.</t>
+  </si>
+  <si>
+    <t>İzmir'in işgali üzerine ilk kurşunu sıkan gazeteci Hasan Tahsin'dir.</t>
+  </si>
+  <si>
+    <t>Amasya Genelgesi ile Kurtuluş Savaşı'nın amacı, gerekçesi ve yöntemi belirlenmiştir.</t>
+  </si>
+  <si>
+    <t>Erzurum Kongresi, toplanış bakımından bölgesel, aldığı kararlar bakımından ulusal bir kongredir.</t>
+  </si>
+  <si>
+    <t>Sivas Kongresi'nde tüm cemiyetler Anadolu ve Rumeli Müdafaa-i Hukuk Cemiyeti adı altında birleştirilmiştir.</t>
+  </si>
+  <si>
+    <t>Misak-ı Milli kararları Son Osmanlı Mebusan Meclisi'nde kabul edilmiştir.</t>
+  </si>
+  <si>
+    <t>TBMM'nin ilk askeri başarısı Ermenilere karşı kazanılan Gümrü Antlaşması'dır.</t>
+  </si>
+  <si>
+    <t>Londra Konferansı ile İtilaf Devletleri TBMM'yi resmen tanımıştır.</t>
+  </si>
+  <si>
+    <t>Sakarya Meydan Muharebesi sonucunda Mustafa Kemal'e Gazilik unvanı ve Mareşallik rütbesi verilmiştir.</t>
+  </si>
+  <si>
+    <t>Büyük Taarruz ile Batı Anadolu Yunan işgalinden temizlenmiştir.</t>
+  </si>
+  <si>
+    <t>Mudanya Ateşkes Antlaşması ile Doğu Trakya, İstanbul ve Boğazlar savaş yapılmadan kurtarılmıştır.</t>
+  </si>
+  <si>
+    <t>Saltanat 1 Kasım 1922'de kaldırılarak Osmanlı Devleti resmen sona ermiştir.</t>
+  </si>
+  <si>
+    <t>Cumhuriyet 29 Ekim 1923'te ilan edilmiştir.</t>
+  </si>
+  <si>
+    <t>Halifelik 3 Mart 1924'te kaldırılmıştır.</t>
+  </si>
+  <si>
+    <t>Tevhid-i Tedrisat Kanunu ile eğitim ve öğretim birleştirilmiştir.</t>
+  </si>
+  <si>
+    <t>Şapka Kanunu 1925 yılında Kastamonu'da tanıtılarak kabul edilmiştir.</t>
+  </si>
+  <si>
+    <t>Medeni Kanun 1926 yılında İsviçre'den örnek alınarak kabul edilmiştir.</t>
+  </si>
+  <si>
+    <t>Kadınlara seçme ve seçilme hakkı ilk olarak 1930'da belediye seçimlerinde verilmiştir.</t>
+  </si>
+  <si>
+    <t>Soyadı Kanunu 1934 yılında kabul edilmiştir.</t>
+  </si>
+  <si>
+    <t>Montrö Boğazlar Sözleşmesi ile Boğazlar Komisyonu kaldırılmış ve egemenlik Türkiye'ye geçmiştir.</t>
+  </si>
+  <si>
+    <t>Hatay, 1939 yılında Türkiye'ye katılmıştır.</t>
+  </si>
+  <si>
+    <t>Çağdaş Türk ve Dünya</t>
+  </si>
+  <si>
+    <t>II. Dünya Savaşı 1939-1945 yılları arasında gerçekleşmiştir.</t>
+  </si>
+  <si>
+    <t>Birleşmiş Milletler 1945 yılında kurulmuştur.</t>
+  </si>
+  <si>
+    <t>NATO 1949 yılında kurulmuştur, Türkiye 1952'de üye olmuştur.</t>
+  </si>
+  <si>
+    <t>Kıbrıs Barış Harekatı 1974 yılında gerçekleştirilmiştir.</t>
+  </si>
+  <si>
+    <t>Soğuk Savaş dönemi, SSCB'nin dağılmasıyla 1991'de sona ermiştir.</t>
+  </si>
+  <si>
+    <t>Avrupa Birliği'nin temeli Roma Antlaşması ile atılmıştır.</t>
+  </si>
+  <si>
+    <t>Türkiye, Avrupa Konseyi'ne 1949 yılında kurucu üye olarak katılmıştır.</t>
+  </si>
+  <si>
+    <t>Osmanlı Devleti'nde ilk denk bütçeyi Tarhuncu Ahmet Paşa hazırlamıştır.</t>
+  </si>
+  <si>
+    <t>Lale Devri'nin ünlü şairi Nedim'dir.</t>
+  </si>
+  <si>
+    <t>Plevne Kahramanı olarak bilinen komutan Gazi Osman Paşa'dır.</t>
+  </si>
+  <si>
+    <t>Mecelle, Ahmet Cevdet Paşa başkanlığındaki bir komisyon tarafından hazırlanmıştır.</t>
+  </si>
+  <si>
+    <t>II. Abdülhamit döneminde Bağdat demiryolu projesi Almanlara verilmiştir.</t>
+  </si>
+  <si>
+    <t>Seyfiye sınıfı, yönetim ve askerlik işlerinden sorumludur (Vezir, Yeniçeri Ağası vb.).</t>
+  </si>
+  <si>
+    <t>İlmiye sınıfı, eğitim, din ve hukuk işlerinden sorumludur (Şeyhülislam, Kadı vb.).</t>
+  </si>
+  <si>
+    <t>Kalemiye sınıfı, bürokrasi ve yazışma işlerinden sorumludur (Nişancı, Defterdar vb.).</t>
+  </si>
+  <si>
+    <t>İstiklal Marşı 12 Mart 1921'de kabul edilmiştir.</t>
+  </si>
+  <si>
+    <t>Menemen Olayı (Kubilay Olayı), Cumhuriyet rejimine karşı çıkan ikinci isyandır.</t>
+  </si>
+  <si>
+    <t>Fiziki Coğrafya</t>
+  </si>
+  <si>
+    <t>Türkiye'nin en yüksek dağı Ağrı Dağı'dır.</t>
+  </si>
+  <si>
+    <t>Türkiye'nin en büyük gölü Van Gölü'dür.</t>
+  </si>
+  <si>
+    <t>Türkiye'nin en uzun akarsuyu Kızılırmak'tır.</t>
+  </si>
+  <si>
+    <t>Türkiye'de en çok yağış alan bölge Karadeniz Bölgesi'dir.</t>
+  </si>
+  <si>
+    <t>Türkiye'de en az yağış alan bölge İç Anadolu Bölgesi'dir.</t>
+  </si>
+  <si>
+    <t>Akdeniz ikliminin bitki örtüsü makidir.</t>
+  </si>
+  <si>
+    <t>Karadeniz ikliminin bitki örtüsü ormandır.</t>
+  </si>
+  <si>
+    <t>Karasal iklimin bitki örtüsü bozkırdır (step).</t>
+  </si>
+  <si>
+    <t>Türkiye'de rüzgar erozyonunun en etkili olduğu bölge İç Anadolu'dur.</t>
+  </si>
+  <si>
+    <t>Türkiye'de heyelan olaylarının en sık görüldüğü bölge Karadeniz'dir.</t>
+  </si>
+  <si>
+    <t>Ege Bölgesi'nde dağlar kıyıya dik uzanır, bu nedenle kı girinti çıkıntısı fazladır.</t>
+  </si>
+  <si>
+    <t>Akdeniz ve Karadeniz'de dağlar kıyıya paralel uzanır, boyuna kıyı tipi görülür.</t>
+  </si>
+  <si>
+    <t>İstanbul ve Çanakkale Boğazları ria tipi kıyıya örnektir.</t>
+  </si>
+  <si>
+    <t>Antalya-Kaş kıyıları dalmaçya tipi kıyıya örnektir.</t>
+  </si>
+  <si>
+    <t>Büyükçekmece ve Küçükçekmece gölleri lagün (kıyı set gölü) örneğidir.</t>
+  </si>
+  <si>
+    <t>Beşeri Coğrafya</t>
+  </si>
+  <si>
+    <t>Türkiye'de nüfusun en yoğun olduğu bölge Marmara Bölgesi'dir.</t>
+  </si>
+  <si>
+    <t>Türkiye'de nüfus yoğunluğunun en az olduğu bölge Doğu Anadolu Bölgesi'dir.</t>
+  </si>
+  <si>
+    <t>Türkiye'de ilk nüfus sayımı 1927 yılında yapılmıştır.</t>
+  </si>
+  <si>
+    <t>Türkiye'de köy altı yerleşmelerinden en yaygın olanı yayladır.</t>
+  </si>
+  <si>
+    <t>Ekonomik Coğrafya</t>
+  </si>
+  <si>
+    <t>Türkiye'de en çok yetiştirilen tarım ürünü buğdaydır.</t>
+  </si>
+  <si>
+    <t>Fındık üretiminde Türkiye dünya birincisidir.</t>
+  </si>
+  <si>
+    <t>İncir üretiminde Aydın ili ilk sıradadır.</t>
+  </si>
+  <si>
+    <t>Kayısı üretiminde Malatya ili ilk sıradadır.</t>
+  </si>
+  <si>
+    <t>Çay tarımı sadece Doğu Karadeniz'de yapılır.</t>
+  </si>
+  <si>
+    <t>Muz tarımı sadece Akdeniz'de (Anamur-Alanya) yapılır.</t>
+  </si>
+  <si>
+    <t>Pamuk, en çok Güneydoğu Anadolu Bölgesi'nde (GAP ile) üretilir.</t>
+  </si>
+  <si>
+    <t>Türkiye'de en çok beslenen hayvan türü koyundur.</t>
+  </si>
+  <si>
+    <t>İpek böcekçiliği en çok Diyarbakır ve çevresinde gelişmiştir (Eskiden Bursa).</t>
+  </si>
+  <si>
+    <t>Arıcılıkta Ordu ve Muğla illeri ön plandadır.</t>
+  </si>
+  <si>
+    <t>Türkiye'nin demir rezervinin en fazla olduğu yer Sivas-Divriği ve Malatya-Hekimhan'dır.</t>
+  </si>
+  <si>
+    <t>Bakır madeni; Kastamonu-Küre, Artvin-Murgul ve Elazığ-Maden'de çıkarılır.</t>
+  </si>
+  <si>
+    <t>Bor mineralleri rezervinde Türkiye dünyada birincisidir.</t>
+  </si>
+  <si>
+    <t>Taş kömürü sadece Zonguldak ve çevresinde çıkarılır.</t>
+  </si>
+  <si>
+    <t>Linyit, Türkiye'de en yaygın bulunan enerji kaynağıdır.</t>
+  </si>
+  <si>
+    <t>Batman, Türkiye'de petrolün çıkarıldığı ve işlendiği (rafineri) ilk yerdir.</t>
+  </si>
+  <si>
+    <t>Türkiye'nin en büyük hidroelektrik barajı Atatürk Barajı'dır.</t>
+  </si>
+  <si>
+    <t>Doğalgaz ile çalışan termik santrallerimizden biri Hamitabat'tır (Kırklareli).</t>
+  </si>
+  <si>
+    <t>Rüzgar enerjisi potansiyeli en yüksek bölgemiz Ege'dir.</t>
+  </si>
+  <si>
+    <t>GAP (Güneydoğu Anadolu Projesi) Türkiye'nin en büyük bölgesel kalkınma projesidir.</t>
+  </si>
+  <si>
+    <t>Zonguldak-Bartın-Karabük projesi (ZBK) kömür ve çeliğe dayalı bir projedir.</t>
+  </si>
+  <si>
+    <t>Doğu Anadolu Projesi (DAP) hayvancılığı geliştirmeyi amaçlar.</t>
+  </si>
+  <si>
+    <t>Konya Ovası Projesi (KOP) sulama ve tarımı geliştirmeyi amaçlar.</t>
+  </si>
+  <si>
+    <t>Türkiye'nin en işlek limanı Ambarlı (İstanbul) ve Mersin limanlarıdır.</t>
+  </si>
+  <si>
+    <t>Hinterlandı en geniş limanımız İstanbul Limanı'dır.</t>
+  </si>
+  <si>
+    <t>Sinop Limanı, hinterlandı dar olduğu için en az gelişen limandır.</t>
+  </si>
+  <si>
+    <t>Türkiye'de demiryolu ağı doğu-batı yönünde uzanır.</t>
+  </si>
+  <si>
+    <t>Yüksek Hızlı Tren (YHT) hattı ilk olarak Ankara-Eskişehir arasında açılmıştır.</t>
+  </si>
+  <si>
+    <t>Mevsimlik işçi göçü en çok tarım, turizm ve inşaat sektörlerinde görülür.</t>
+  </si>
+  <si>
+    <t>Volkanik dağlarımızdan biri olan Erciyes, İç Anadolu Bölgesi'ndedir.</t>
+  </si>
+  <si>
+    <t>Karstik araziler en çok Akdeniz Bölgesi'nde (Teke ve Taşeli platoları) yaygındır.</t>
+  </si>
+  <si>
+    <t>Temel Hukuk</t>
+  </si>
+  <si>
+    <t>Hukuk kurallarının yaptırımı maddidir (devlet gücü).</t>
+  </si>
+  <si>
+    <t>Sosyal hayatı düzenleyen kurallar; din, ahlak, görgü ve hukuk kurallarıdır.</t>
+  </si>
+  <si>
+    <t>Kişinin kendi vicdanına karşı sorumluluğuna sübjektif ahlak denir.</t>
+  </si>
+  <si>
+    <t>Bir ülkede belli bir zamanda yürürlükte olan yazılı ve yazısız hukuk kurallarının tümüne Pozitif Hukuk (Müspet Hukuk) denir.</t>
+  </si>
+  <si>
+    <t>Sadece yazılı hukuk kurallarına Mevzu Hukuk denir.</t>
+  </si>
+  <si>
+    <t>Hukuk boşluğu, kanunda ve örf adette kural bulunmaması durumudur.</t>
+  </si>
+  <si>
+    <t>Kanun boşluğu, kanunda somut olaya uygulanacak hüküm bulunmamasıdır.</t>
+  </si>
+  <si>
+    <t>Hakim, hukuk boşluğu durumunda hukuk yaratır.</t>
+  </si>
+  <si>
+    <t>Hak ehliyeti, sağ ve tam doğmak koşuluyla ana rahmine düşüldüğü an başlar.</t>
+  </si>
+  <si>
+    <t>Fiil ehliyetinin şartları; ergin olmak, ayırt etme gücüne sahip olmak ve kısıtlı olmamaktır.</t>
+  </si>
+  <si>
+    <t>Olağan evlenme yaşı, veli izniyle 17 yaşın doldurulmasıdır.</t>
+  </si>
+  <si>
+    <t>Olağanüstü evlenme yaşı, mahkeme kararıyla 16 yaşın doldurulmasıdır.</t>
+  </si>
+  <si>
+    <t>Gaiplik kararı, ölüm tehlikesi içinde kaybolmada 1 yıl, uzun süre haber alamamada 5 yıl sonra istenebilir.</t>
+  </si>
+  <si>
+    <t>Türkiye Cumhuriyeti'nin ilk anayasası 1921 Anayasası'dır (Teşkilat-ı Esasiye).</t>
+  </si>
+  <si>
+    <t>Cumhuriyetin ilanı ve laiklik ilkesi 1924 Anayasası döneminde gerçekleşmiştir.</t>
+  </si>
+  <si>
+    <t>1961 Anayasası, kuvvetler ayrılığını ve sosyal devleti benimseyen ilk anayasadır.</t>
+  </si>
+  <si>
+    <t>1982 Anayasası, Kenan Evren başkanlığındaki Danışma Meclisi tarafından hazırlanmıştır.</t>
+  </si>
+  <si>
+    <t>Anayasamızın ilk 3 maddesi değiştirilemez ve değiştirilmesi teklif dahi edilemez.</t>
+  </si>
+  <si>
+    <t>Türkiye Devleti bir Cumhuriyettir (Madde 1).</t>
+  </si>
+  <si>
+    <t>Egemenlik kayıtsız şartsız milletindir.</t>
+  </si>
+  <si>
+    <t>Yasama yetkisi Türk Milleti adına Türkiye Büyük Millet Meclisi'nindir (TBMM).</t>
+  </si>
+  <si>
+    <t>Yürütme yetkisi ve görevi Cumhurbaşkanı tarafından kullanılır.</t>
+  </si>
+  <si>
+    <t>Yargı yetkisi Türk Milleti adına bağımsız ve tarafsız mahkemelerce kullanılır.</t>
+  </si>
+  <si>
+    <t>Bir yasama yılı 1 Ekim'de başlar.</t>
+  </si>
+  <si>
+    <t>TBMM üye sayısı 600'dür.</t>
+  </si>
+  <si>
+    <t>Cumhurbaşkanı halk tarafından 5 yıllığına seçilir.</t>
+  </si>
+  <si>
+    <t>Bir kişi en fazla iki kez Cumhurbaşkanı seçilebilir.</t>
+  </si>
+  <si>
+    <t>Cumhurbaşkanlığı Kararnamesi, olağan dönemlerde kanun hükmündedir (ancak kanunla çelişirse kanun esas alınır).</t>
+  </si>
+  <si>
+    <t>Milli Güvenlik Kurulu'na (MGK) Cumhurbaşkanı başkanlık eder.</t>
+  </si>
+  <si>
+    <t>Devlet Denetleme Kurulu (DDK) Cumhurbaşkanlığına bağlıdır.</t>
+  </si>
+  <si>
+    <t>İdare Hukuku</t>
+  </si>
+  <si>
+    <t>İdare hukukunun temel amacı kamu yararını sağlamaktır.</t>
+  </si>
+  <si>
+    <t>Merkezi idare; Başkent teşkilatı ve Taşra teşkilatından oluşur.</t>
+  </si>
+  <si>
+    <t>İl idaresinin başı Validir.</t>
+  </si>
+  <si>
+    <t>Vali, istisnai memurdur ve Cumhurbaşkanı kararıyla atanır.</t>
+  </si>
+  <si>
+    <t>İlçe idaresinin başı Kaymakamdır.</t>
+  </si>
+  <si>
+    <t>Yerel yönetimler; İl Özel İdaresi, Belediye ve Köy'dür.</t>
+  </si>
+  <si>
+    <t>Belediye kurulması için nüfusun en az 5000 olması gerekir.</t>
+  </si>
+  <si>
+    <t>Büyükşehir Belediyesi kurulması için nüfusun en az 750.000 olması gerekir.</t>
+  </si>
+  <si>
+    <t>Köy idaresinin başı Muhtardır.</t>
+  </si>
+  <si>
+    <t>Memurlara verilen disiplin cezaları; uyarma, kınama, aylıktan kesme, kademe ilerlemesinin durdurulması ve devlet memurluğundan çıkarmadır.</t>
+  </si>
+  <si>
+    <t>Kamulaştırma (İstimlak), devletin özel mülkiyetteki taşınmaza kamu yararı için el koymasıdır.</t>
+  </si>
+  <si>
+    <t>İstimval, olağanüstü durumlarda taşınırlara el konulmasıdır.</t>
+  </si>
+  <si>
+    <t>Yargıtay, adli yargının en üst merciidir.</t>
+  </si>
+  <si>
+    <t>Danıştay, idari yargının en üst merciidir.</t>
+  </si>
+  <si>
+    <t>Uyuşmazlık Mahkemesi, adli ve idari yargı arasındaki görev uyuşmazlıklarını çözer.</t>
+  </si>
+  <si>
+    <t>Hakimler ve Savcılar Kurulu (HSK) 13 üyeden oluşur.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="162"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="162"/>
@@ -494,10 +939,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -832,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF510A4F-D7B2-CE48-8A90-163E9C2B56A8}">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D250"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" customWidth="1"/>
@@ -842,1417 +1286,3503 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24">
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="1" t="s">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="1" t="s">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26">
         <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27">
         <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28">
         <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
+      <c r="A29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29">
         <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="1" t="s">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30">
         <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="1" t="s">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31">
         <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="1" t="s">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32">
         <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="A33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>44</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33">
         <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="1" t="s">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34">
         <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="1" t="s">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
         <v>47</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35">
         <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="1" t="s">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
         <v>46</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
         <v>48</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36">
         <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="1" t="s">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37">
         <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" s="1" t="s">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s">
         <v>51</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38">
         <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" s="1" t="s">
+      <c r="A39" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" t="s">
         <v>50</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39">
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" s="1" t="s">
+      <c r="A40" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" t="s">
         <v>50</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" t="s">
         <v>53</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40">
         <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" s="1" t="s">
+      <c r="A41" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" t="s">
         <v>54</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41">
         <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B42" s="1" t="s">
+      <c r="A42" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" t="s">
         <v>56</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42">
         <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B43" s="1" t="s">
+      <c r="A43" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s">
         <v>57</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43">
         <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B44" s="1" t="s">
+      <c r="A44" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" t="s">
         <v>59</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44">
         <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B45" s="1" t="s">
+      <c r="A45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" t="s">
         <v>58</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" t="s">
         <v>60</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45">
         <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B46" s="1" t="s">
+      <c r="A46" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" t="s">
         <v>58</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" t="s">
         <v>61</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46">
         <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" s="1" t="s">
+      <c r="A47" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" t="s">
         <v>58</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47">
         <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B48" s="1" t="s">
+      <c r="A48" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" t="s">
         <v>63</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48">
         <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B49" s="1" t="s">
+      <c r="A49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" t="s">
         <v>58</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" t="s">
         <v>64</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49">
         <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B50" s="1" t="s">
+      <c r="A50" t="s">
+        <v>35</v>
+      </c>
+      <c r="B50" t="s">
         <v>65</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" t="s">
         <v>66</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D50">
         <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B51" s="1" t="s">
+      <c r="A51" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" t="s">
         <v>68</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D51">
         <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B52" s="1" t="s">
+      <c r="A52" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" t="s">
         <v>70</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" t="s">
         <v>71</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D52">
         <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B53" s="1" t="s">
+      <c r="A53" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" t="s">
         <v>70</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" t="s">
         <v>72</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D53">
         <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B54" s="1" t="s">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" t="s">
         <v>70</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" t="s">
         <v>73</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D54">
         <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B55" s="1" t="s">
+      <c r="A55" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55" t="s">
         <v>70</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" t="s">
         <v>74</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55">
         <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B56" s="1" t="s">
+      <c r="A56" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" t="s">
         <v>75</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" t="s">
         <v>76</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D56">
         <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57" s="1" t="s">
+      <c r="A57" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" t="s">
         <v>75</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" t="s">
         <v>77</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D57">
         <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B58" s="1" t="s">
+      <c r="A58" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" t="s">
         <v>75</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" t="s">
         <v>78</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D58">
         <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B59" s="1" t="s">
+      <c r="A59" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" t="s">
         <v>79</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" t="s">
         <v>80</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D59">
         <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B60" s="1" t="s">
+      <c r="A60" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" t="s">
         <v>79</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" t="s">
         <v>81</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D60">
         <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B61" s="1" t="s">
+      <c r="A61" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" t="s">
         <v>79</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" t="s">
         <v>82</v>
       </c>
-      <c r="D61" s="1">
+      <c r="D61">
         <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B62" s="1" t="s">
+      <c r="A62" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" t="s">
         <v>79</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" t="s">
         <v>83</v>
       </c>
-      <c r="D62" s="1">
+      <c r="D62">
         <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" s="1" t="s">
+      <c r="A63" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" t="s">
         <v>79</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" t="s">
         <v>84</v>
       </c>
-      <c r="D63" s="1">
+      <c r="D63">
         <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B64" s="1" t="s">
+      <c r="A64" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64" t="s">
         <v>85</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" t="s">
         <v>86</v>
       </c>
-      <c r="D64" s="1">
+      <c r="D64">
         <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B65" s="1" t="s">
+      <c r="A65" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" t="s">
         <v>85</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" t="s">
         <v>87</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65">
         <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B66" s="1" t="s">
+      <c r="A66" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66" t="s">
         <v>85</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" t="s">
         <v>88</v>
       </c>
-      <c r="D66" s="1">
+      <c r="D66">
         <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B67" s="1" t="s">
+      <c r="A67" t="s">
+        <v>69</v>
+      </c>
+      <c r="B67" t="s">
         <v>85</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" t="s">
         <v>89</v>
       </c>
-      <c r="D67" s="1">
+      <c r="D67">
         <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B68" s="1" t="s">
+      <c r="A68" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68" t="s">
         <v>90</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" t="s">
         <v>91</v>
       </c>
-      <c r="D68" s="1">
+      <c r="D68">
         <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B69" s="1" t="s">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" t="s">
         <v>90</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" t="s">
         <v>92</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D69">
         <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B70" s="1" t="s">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
         <v>90</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" t="s">
         <v>93</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D70">
         <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B71" s="1" t="s">
+      <c r="A71" t="s">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" t="s">
         <v>95</v>
       </c>
-      <c r="D71" s="1">
+      <c r="D71">
         <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B72" s="1" t="s">
+      <c r="A72" t="s">
+        <v>69</v>
+      </c>
+      <c r="B72" t="s">
         <v>94</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" t="s">
         <v>96</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D72">
         <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B73" s="1" t="s">
+      <c r="A73" t="s">
+        <v>69</v>
+      </c>
+      <c r="B73" t="s">
         <v>94</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" t="s">
         <v>97</v>
       </c>
-      <c r="D73" s="1">
+      <c r="D73">
         <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B74" s="1" t="s">
+      <c r="A74" t="s">
+        <v>69</v>
+      </c>
+      <c r="B74" t="s">
         <v>94</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" t="s">
         <v>98</v>
       </c>
-      <c r="D74" s="1">
+      <c r="D74">
         <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B75" s="1" t="s">
+      <c r="A75" t="s">
+        <v>69</v>
+      </c>
+      <c r="B75" t="s">
         <v>94</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" t="s">
         <v>99</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D75">
         <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B76" s="1" t="s">
+      <c r="A76" t="s">
+        <v>69</v>
+      </c>
+      <c r="B76" t="s">
         <v>94</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" t="s">
         <v>100</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D76">
         <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="1" t="s">
+      <c r="A77" t="s">
         <v>101</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" t="s">
         <v>0</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" t="s">
         <v>102</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D77">
         <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="1" t="s">
+      <c r="A78" t="s">
         <v>101</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" t="s">
         <v>0</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" t="s">
         <v>103</v>
       </c>
-      <c r="D78" s="1">
+      <c r="D78">
         <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="1" t="s">
+      <c r="A79" t="s">
         <v>101</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" t="s">
         <v>104</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" t="s">
         <v>105</v>
       </c>
-      <c r="D79" s="1">
+      <c r="D79">
         <v>15</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="1" t="s">
+      <c r="A80" t="s">
         <v>101</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" t="s">
         <v>106</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" t="s">
         <v>107</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D80">
         <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
+      <c r="A81" t="s">
         <v>101</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" t="s">
         <v>108</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" t="s">
         <v>109</v>
       </c>
-      <c r="D81" s="1">
+      <c r="D81">
         <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
+      <c r="A82" t="s">
         <v>101</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" t="s">
         <v>110</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" t="s">
         <v>111</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D82">
         <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="1" t="s">
+      <c r="A83" t="s">
         <v>101</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" t="s">
         <v>110</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" t="s">
         <v>112</v>
       </c>
-      <c r="D83" s="1">
+      <c r="D83">
         <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="1" t="s">
+      <c r="A84" t="s">
         <v>101</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C84" s="1" t="s">
+      <c r="B84" t="s">
+        <v>35</v>
+      </c>
+      <c r="C84" t="s">
         <v>113</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D84">
         <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
+      <c r="A85" t="s">
         <v>101</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C85" s="1" t="s">
+      <c r="B85" t="s">
+        <v>35</v>
+      </c>
+      <c r="C85" t="s">
         <v>114</v>
       </c>
-      <c r="D85" s="1">
+      <c r="D85">
         <v>12</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="1" t="s">
+      <c r="A86" t="s">
         <v>101</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" t="s">
         <v>115</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" t="s">
         <v>116</v>
       </c>
-      <c r="D86" s="1">
+      <c r="D86">
         <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="1" t="s">
+      <c r="A87" t="s">
         <v>101</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" t="s">
         <v>115</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" t="s">
         <v>117</v>
       </c>
-      <c r="D87" s="1">
+      <c r="D87">
         <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="1" t="s">
+      <c r="A88" t="s">
         <v>101</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" t="s">
         <v>115</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" t="s">
         <v>118</v>
       </c>
-      <c r="D88" s="1">
+      <c r="D88">
         <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="1" t="s">
+      <c r="A89" t="s">
         <v>101</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" t="s">
         <v>119</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" t="s">
         <v>120</v>
       </c>
-      <c r="D89" s="1">
+      <c r="D89">
         <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="1" t="s">
+      <c r="A90" t="s">
         <v>101</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C90" s="1" t="s">
+      <c r="B90" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" t="s">
         <v>121</v>
       </c>
-      <c r="D90" s="1">
+      <c r="D90">
         <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="1" t="s">
+      <c r="A91" t="s">
         <v>101</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" t="s">
         <v>0</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" t="s">
         <v>122</v>
       </c>
-      <c r="D91" s="1">
+      <c r="D91">
         <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
+      <c r="A92" t="s">
         <v>101</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" t="s">
         <v>123</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" t="s">
         <v>124</v>
       </c>
-      <c r="D92" s="1">
+      <c r="D92">
         <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="1" t="s">
+      <c r="A93" t="s">
         <v>101</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" t="s">
         <v>123</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" t="s">
         <v>125</v>
       </c>
-      <c r="D93" s="1">
+      <c r="D93">
         <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="1" t="s">
+      <c r="A94" t="s">
         <v>101</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" t="s">
         <v>106</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" t="s">
         <v>126</v>
       </c>
-      <c r="D94" s="1">
+      <c r="D94">
         <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="1" t="s">
+      <c r="A95" t="s">
         <v>101</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" t="s">
         <v>106</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" t="s">
         <v>127</v>
       </c>
-      <c r="D95" s="1">
+      <c r="D95">
         <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="1" t="s">
+      <c r="A96" t="s">
         <v>101</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B96" t="s">
         <v>128</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" t="s">
         <v>129</v>
       </c>
-      <c r="D96" s="1">
+      <c r="D96">
         <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="1" t="s">
+      <c r="A97" t="s">
         <v>101</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B97" t="s">
         <v>128</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" t="s">
         <v>130</v>
       </c>
-      <c r="D97" s="1">
+      <c r="D97">
         <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="1" t="s">
+      <c r="A98" t="s">
         <v>101</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" t="s">
         <v>128</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" t="s">
         <v>131</v>
       </c>
-      <c r="D98" s="1">
+      <c r="D98">
         <v>12</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="1" t="s">
+      <c r="A99" t="s">
         <v>101</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" t="s">
         <v>128</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" t="s">
         <v>132</v>
       </c>
-      <c r="D99" s="1">
+      <c r="D99">
         <v>15</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" s="1" t="s">
+      <c r="A100" t="s">
         <v>101</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" t="s">
         <v>128</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" t="s">
         <v>133</v>
       </c>
-      <c r="D100" s="1">
+      <c r="D100">
         <v>12</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" s="1" t="s">
+      <c r="A101" t="s">
         <v>101</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" t="s">
         <v>128</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" t="s">
         <v>134</v>
       </c>
-      <c r="D101" s="1">
-        <v>15</v>
+      <c r="D101">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>5</v>
+      </c>
+      <c r="B102" t="s">
+        <v>15</v>
+      </c>
+      <c r="C102" t="s">
+        <v>135</v>
+      </c>
+      <c r="D102">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>5</v>
+      </c>
+      <c r="B103" t="s">
+        <v>15</v>
+      </c>
+      <c r="C103" t="s">
+        <v>136</v>
+      </c>
+      <c r="D103">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>5</v>
+      </c>
+      <c r="B104" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104" t="s">
+        <v>137</v>
+      </c>
+      <c r="D104">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>5</v>
+      </c>
+      <c r="B105" t="s">
+        <v>15</v>
+      </c>
+      <c r="C105" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>5</v>
+      </c>
+      <c r="B106" t="s">
+        <v>15</v>
+      </c>
+      <c r="C106" t="s">
+        <v>138</v>
+      </c>
+      <c r="D106">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>5</v>
+      </c>
+      <c r="B107" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107" t="s">
+        <v>139</v>
+      </c>
+      <c r="D107">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>5</v>
+      </c>
+      <c r="B108" t="s">
+        <v>15</v>
+      </c>
+      <c r="C108" t="s">
+        <v>140</v>
+      </c>
+      <c r="D108">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>5</v>
+      </c>
+      <c r="B109" t="s">
+        <v>15</v>
+      </c>
+      <c r="C109" t="s">
+        <v>141</v>
+      </c>
+      <c r="D109">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>5</v>
+      </c>
+      <c r="B110" t="s">
+        <v>15</v>
+      </c>
+      <c r="C110" t="s">
+        <v>142</v>
+      </c>
+      <c r="D110">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>5</v>
+      </c>
+      <c r="B111" t="s">
+        <v>15</v>
+      </c>
+      <c r="C111" t="s">
+        <v>143</v>
+      </c>
+      <c r="D111">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>5</v>
+      </c>
+      <c r="B112" t="s">
+        <v>144</v>
+      </c>
+      <c r="C112" t="s">
+        <v>145</v>
+      </c>
+      <c r="D112">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>5</v>
+      </c>
+      <c r="B113" t="s">
+        <v>144</v>
+      </c>
+      <c r="C113" t="s">
+        <v>146</v>
+      </c>
+      <c r="D113">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>5</v>
+      </c>
+      <c r="B114" t="s">
+        <v>144</v>
+      </c>
+      <c r="C114" t="s">
+        <v>147</v>
+      </c>
+      <c r="D114">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>5</v>
+      </c>
+      <c r="B115" t="s">
+        <v>144</v>
+      </c>
+      <c r="C115" t="s">
+        <v>148</v>
+      </c>
+      <c r="D115">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>5</v>
+      </c>
+      <c r="B116" t="s">
+        <v>144</v>
+      </c>
+      <c r="C116" t="s">
+        <v>149</v>
+      </c>
+      <c r="D116">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>5</v>
+      </c>
+      <c r="B117" t="s">
+        <v>144</v>
+      </c>
+      <c r="C117" t="s">
+        <v>150</v>
+      </c>
+      <c r="D117">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>5</v>
+      </c>
+      <c r="B118" t="s">
+        <v>144</v>
+      </c>
+      <c r="C118" t="s">
+        <v>151</v>
+      </c>
+      <c r="D118">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>5</v>
+      </c>
+      <c r="B119" t="s">
+        <v>144</v>
+      </c>
+      <c r="C119" t="s">
+        <v>152</v>
+      </c>
+      <c r="D119">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>5</v>
+      </c>
+      <c r="B120" t="s">
+        <v>144</v>
+      </c>
+      <c r="C120" t="s">
+        <v>153</v>
+      </c>
+      <c r="D120">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>5</v>
+      </c>
+      <c r="B121" t="s">
+        <v>144</v>
+      </c>
+      <c r="C121" t="s">
+        <v>154</v>
+      </c>
+      <c r="D121">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>5</v>
+      </c>
+      <c r="B122" t="s">
+        <v>144</v>
+      </c>
+      <c r="C122" t="s">
+        <v>155</v>
+      </c>
+      <c r="D122">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>5</v>
+      </c>
+      <c r="B123" t="s">
+        <v>144</v>
+      </c>
+      <c r="C123" t="s">
+        <v>156</v>
+      </c>
+      <c r="D123">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>5</v>
+      </c>
+      <c r="B124" t="s">
+        <v>144</v>
+      </c>
+      <c r="C124" t="s">
+        <v>157</v>
+      </c>
+      <c r="D124">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>5</v>
+      </c>
+      <c r="B125" t="s">
+        <v>144</v>
+      </c>
+      <c r="C125" t="s">
+        <v>28</v>
+      </c>
+      <c r="D125">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>5</v>
+      </c>
+      <c r="B126" t="s">
+        <v>144</v>
+      </c>
+      <c r="C126" t="s">
+        <v>158</v>
+      </c>
+      <c r="D126">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>5</v>
+      </c>
+      <c r="B127" t="s">
+        <v>144</v>
+      </c>
+      <c r="C127" t="s">
+        <v>159</v>
+      </c>
+      <c r="D127">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>5</v>
+      </c>
+      <c r="B128" t="s">
+        <v>144</v>
+      </c>
+      <c r="C128" t="s">
+        <v>160</v>
+      </c>
+      <c r="D128">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>5</v>
+      </c>
+      <c r="B129" t="s">
+        <v>144</v>
+      </c>
+      <c r="C129" t="s">
+        <v>161</v>
+      </c>
+      <c r="D129">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>5</v>
+      </c>
+      <c r="B130" t="s">
+        <v>144</v>
+      </c>
+      <c r="C130" t="s">
+        <v>162</v>
+      </c>
+      <c r="D130">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>5</v>
+      </c>
+      <c r="B131" t="s">
+        <v>144</v>
+      </c>
+      <c r="C131" t="s">
+        <v>163</v>
+      </c>
+      <c r="D131">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>5</v>
+      </c>
+      <c r="B132" t="s">
+        <v>144</v>
+      </c>
+      <c r="C132" t="s">
+        <v>164</v>
+      </c>
+      <c r="D132">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>5</v>
+      </c>
+      <c r="B133" t="s">
+        <v>144</v>
+      </c>
+      <c r="C133" t="s">
+        <v>165</v>
+      </c>
+      <c r="D133">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>5</v>
+      </c>
+      <c r="B134" t="s">
+        <v>144</v>
+      </c>
+      <c r="C134" t="s">
+        <v>166</v>
+      </c>
+      <c r="D134">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>5</v>
+      </c>
+      <c r="B135" t="s">
+        <v>167</v>
+      </c>
+      <c r="C135" t="s">
+        <v>168</v>
+      </c>
+      <c r="D135">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>5</v>
+      </c>
+      <c r="B136" t="s">
+        <v>167</v>
+      </c>
+      <c r="C136" t="s">
+        <v>169</v>
+      </c>
+      <c r="D136">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>5</v>
+      </c>
+      <c r="B137" t="s">
+        <v>167</v>
+      </c>
+      <c r="C137" t="s">
+        <v>170</v>
+      </c>
+      <c r="D137">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>5</v>
+      </c>
+      <c r="B138" t="s">
+        <v>167</v>
+      </c>
+      <c r="C138" t="s">
+        <v>171</v>
+      </c>
+      <c r="D138">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>5</v>
+      </c>
+      <c r="B139" t="s">
+        <v>167</v>
+      </c>
+      <c r="C139" t="s">
+        <v>172</v>
+      </c>
+      <c r="D139">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>5</v>
+      </c>
+      <c r="B140" t="s">
+        <v>167</v>
+      </c>
+      <c r="C140" t="s">
+        <v>173</v>
+      </c>
+      <c r="D140">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>5</v>
+      </c>
+      <c r="B141" t="s">
+        <v>167</v>
+      </c>
+      <c r="C141" t="s">
+        <v>174</v>
+      </c>
+      <c r="D141">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>5</v>
+      </c>
+      <c r="B142" t="s">
+        <v>15</v>
+      </c>
+      <c r="C142" t="s">
+        <v>175</v>
+      </c>
+      <c r="D142">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>5</v>
+      </c>
+      <c r="B143" t="s">
+        <v>15</v>
+      </c>
+      <c r="C143" t="s">
+        <v>176</v>
+      </c>
+      <c r="D143">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>5</v>
+      </c>
+      <c r="B144" t="s">
+        <v>15</v>
+      </c>
+      <c r="C144" t="s">
+        <v>177</v>
+      </c>
+      <c r="D144">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>5</v>
+      </c>
+      <c r="B145" t="s">
+        <v>15</v>
+      </c>
+      <c r="C145" t="s">
+        <v>178</v>
+      </c>
+      <c r="D145">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>5</v>
+      </c>
+      <c r="B146" t="s">
+        <v>15</v>
+      </c>
+      <c r="C146" t="s">
+        <v>179</v>
+      </c>
+      <c r="D146">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>5</v>
+      </c>
+      <c r="B147" t="s">
+        <v>15</v>
+      </c>
+      <c r="C147" t="s">
+        <v>180</v>
+      </c>
+      <c r="D147">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>5</v>
+      </c>
+      <c r="B148" t="s">
+        <v>15</v>
+      </c>
+      <c r="C148" t="s">
+        <v>181</v>
+      </c>
+      <c r="D148">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>5</v>
+      </c>
+      <c r="B149" t="s">
+        <v>15</v>
+      </c>
+      <c r="C149" t="s">
+        <v>182</v>
+      </c>
+      <c r="D149">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>5</v>
+      </c>
+      <c r="B150" t="s">
+        <v>144</v>
+      </c>
+      <c r="C150" t="s">
+        <v>183</v>
+      </c>
+      <c r="D150">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>5</v>
+      </c>
+      <c r="B151" t="s">
+        <v>144</v>
+      </c>
+      <c r="C151" t="s">
+        <v>184</v>
+      </c>
+      <c r="D151">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>35</v>
+      </c>
+      <c r="B152" t="s">
+        <v>185</v>
+      </c>
+      <c r="C152" t="s">
+        <v>186</v>
+      </c>
+      <c r="D152">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>35</v>
+      </c>
+      <c r="B153" t="s">
+        <v>185</v>
+      </c>
+      <c r="C153" t="s">
+        <v>187</v>
+      </c>
+      <c r="D153">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>35</v>
+      </c>
+      <c r="B154" t="s">
+        <v>185</v>
+      </c>
+      <c r="C154" t="s">
+        <v>188</v>
+      </c>
+      <c r="D154">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>35</v>
+      </c>
+      <c r="B155" t="s">
+        <v>185</v>
+      </c>
+      <c r="C155" t="s">
+        <v>189</v>
+      </c>
+      <c r="D155">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>35</v>
+      </c>
+      <c r="B156" t="s">
+        <v>185</v>
+      </c>
+      <c r="C156" t="s">
+        <v>190</v>
+      </c>
+      <c r="D156">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>35</v>
+      </c>
+      <c r="B157" t="s">
+        <v>185</v>
+      </c>
+      <c r="C157" t="s">
+        <v>191</v>
+      </c>
+      <c r="D157">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>35</v>
+      </c>
+      <c r="B158" t="s">
+        <v>185</v>
+      </c>
+      <c r="C158" t="s">
+        <v>192</v>
+      </c>
+      <c r="D158">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>35</v>
+      </c>
+      <c r="B159" t="s">
+        <v>185</v>
+      </c>
+      <c r="C159" t="s">
+        <v>193</v>
+      </c>
+      <c r="D159">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>35</v>
+      </c>
+      <c r="B160" t="s">
+        <v>185</v>
+      </c>
+      <c r="C160" t="s">
+        <v>194</v>
+      </c>
+      <c r="D160">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>35</v>
+      </c>
+      <c r="B161" t="s">
+        <v>185</v>
+      </c>
+      <c r="C161" t="s">
+        <v>195</v>
+      </c>
+      <c r="D161">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>35</v>
+      </c>
+      <c r="B162" t="s">
+        <v>185</v>
+      </c>
+      <c r="C162" t="s">
+        <v>196</v>
+      </c>
+      <c r="D162">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>35</v>
+      </c>
+      <c r="B163" t="s">
+        <v>185</v>
+      </c>
+      <c r="C163" t="s">
+        <v>197</v>
+      </c>
+      <c r="D163">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>35</v>
+      </c>
+      <c r="B164" t="s">
+        <v>185</v>
+      </c>
+      <c r="C164" t="s">
+        <v>198</v>
+      </c>
+      <c r="D164">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>35</v>
+      </c>
+      <c r="B165" t="s">
+        <v>185</v>
+      </c>
+      <c r="C165" t="s">
+        <v>199</v>
+      </c>
+      <c r="D165">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>35</v>
+      </c>
+      <c r="B166" t="s">
+        <v>185</v>
+      </c>
+      <c r="C166" t="s">
+        <v>200</v>
+      </c>
+      <c r="D166">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>35</v>
+      </c>
+      <c r="B167" t="s">
+        <v>201</v>
+      </c>
+      <c r="C167" t="s">
+        <v>202</v>
+      </c>
+      <c r="D167">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>35</v>
+      </c>
+      <c r="B168" t="s">
+        <v>201</v>
+      </c>
+      <c r="C168" t="s">
+        <v>203</v>
+      </c>
+      <c r="D168">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>35</v>
+      </c>
+      <c r="B169" t="s">
+        <v>201</v>
+      </c>
+      <c r="C169" t="s">
+        <v>204</v>
+      </c>
+      <c r="D169">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>35</v>
+      </c>
+      <c r="B170" t="s">
+        <v>201</v>
+      </c>
+      <c r="C170" t="s">
+        <v>205</v>
+      </c>
+      <c r="D170">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>35</v>
+      </c>
+      <c r="B171" t="s">
+        <v>206</v>
+      </c>
+      <c r="C171" t="s">
+        <v>207</v>
+      </c>
+      <c r="D171">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>35</v>
+      </c>
+      <c r="B172" t="s">
+        <v>206</v>
+      </c>
+      <c r="C172" t="s">
+        <v>208</v>
+      </c>
+      <c r="D172">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>35</v>
+      </c>
+      <c r="B173" t="s">
+        <v>206</v>
+      </c>
+      <c r="C173" t="s">
+        <v>209</v>
+      </c>
+      <c r="D173">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>35</v>
+      </c>
+      <c r="B174" t="s">
+        <v>206</v>
+      </c>
+      <c r="C174" t="s">
+        <v>210</v>
+      </c>
+      <c r="D174">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>35</v>
+      </c>
+      <c r="B175" t="s">
+        <v>206</v>
+      </c>
+      <c r="C175" t="s">
+        <v>211</v>
+      </c>
+      <c r="D175">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>35</v>
+      </c>
+      <c r="B176" t="s">
+        <v>206</v>
+      </c>
+      <c r="C176" t="s">
+        <v>212</v>
+      </c>
+      <c r="D176">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>35</v>
+      </c>
+      <c r="B177" t="s">
+        <v>206</v>
+      </c>
+      <c r="C177" t="s">
+        <v>213</v>
+      </c>
+      <c r="D177">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>35</v>
+      </c>
+      <c r="B178" t="s">
+        <v>206</v>
+      </c>
+      <c r="C178" t="s">
+        <v>214</v>
+      </c>
+      <c r="D178">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>35</v>
+      </c>
+      <c r="B179" t="s">
+        <v>206</v>
+      </c>
+      <c r="C179" t="s">
+        <v>215</v>
+      </c>
+      <c r="D179">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>35</v>
+      </c>
+      <c r="B180" t="s">
+        <v>206</v>
+      </c>
+      <c r="C180" t="s">
+        <v>216</v>
+      </c>
+      <c r="D180">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>35</v>
+      </c>
+      <c r="B181" t="s">
+        <v>206</v>
+      </c>
+      <c r="C181" t="s">
+        <v>217</v>
+      </c>
+      <c r="D181">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>35</v>
+      </c>
+      <c r="B182" t="s">
+        <v>206</v>
+      </c>
+      <c r="C182" t="s">
+        <v>218</v>
+      </c>
+      <c r="D182">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>35</v>
+      </c>
+      <c r="B183" t="s">
+        <v>206</v>
+      </c>
+      <c r="C183" t="s">
+        <v>219</v>
+      </c>
+      <c r="D183">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>35</v>
+      </c>
+      <c r="B184" t="s">
+        <v>206</v>
+      </c>
+      <c r="C184" t="s">
+        <v>220</v>
+      </c>
+      <c r="D184">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>35</v>
+      </c>
+      <c r="B185" t="s">
+        <v>206</v>
+      </c>
+      <c r="C185" t="s">
+        <v>221</v>
+      </c>
+      <c r="D185">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
+        <v>35</v>
+      </c>
+      <c r="B186" t="s">
+        <v>206</v>
+      </c>
+      <c r="C186" t="s">
+        <v>222</v>
+      </c>
+      <c r="D186">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>35</v>
+      </c>
+      <c r="B187" t="s">
+        <v>206</v>
+      </c>
+      <c r="C187" t="s">
+        <v>223</v>
+      </c>
+      <c r="D187">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>35</v>
+      </c>
+      <c r="B188" t="s">
+        <v>206</v>
+      </c>
+      <c r="C188" t="s">
+        <v>224</v>
+      </c>
+      <c r="D188">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
+        <v>35</v>
+      </c>
+      <c r="B189" t="s">
+        <v>206</v>
+      </c>
+      <c r="C189" t="s">
+        <v>225</v>
+      </c>
+      <c r="D189">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
+        <v>35</v>
+      </c>
+      <c r="B190" t="s">
+        <v>206</v>
+      </c>
+      <c r="C190" t="s">
+        <v>226</v>
+      </c>
+      <c r="D190">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>35</v>
+      </c>
+      <c r="B191" t="s">
+        <v>206</v>
+      </c>
+      <c r="C191" t="s">
+        <v>227</v>
+      </c>
+      <c r="D191">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>35</v>
+      </c>
+      <c r="B192" t="s">
+        <v>206</v>
+      </c>
+      <c r="C192" t="s">
+        <v>228</v>
+      </c>
+      <c r="D192">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>35</v>
+      </c>
+      <c r="B193" t="s">
+        <v>206</v>
+      </c>
+      <c r="C193" t="s">
+        <v>229</v>
+      </c>
+      <c r="D193">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>35</v>
+      </c>
+      <c r="B194" t="s">
+        <v>206</v>
+      </c>
+      <c r="C194" t="s">
+        <v>230</v>
+      </c>
+      <c r="D194">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>35</v>
+      </c>
+      <c r="B195" t="s">
+        <v>206</v>
+      </c>
+      <c r="C195" t="s">
+        <v>231</v>
+      </c>
+      <c r="D195">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>35</v>
+      </c>
+      <c r="B196" t="s">
+        <v>206</v>
+      </c>
+      <c r="C196" t="s">
+        <v>232</v>
+      </c>
+      <c r="D196">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>35</v>
+      </c>
+      <c r="B197" t="s">
+        <v>206</v>
+      </c>
+      <c r="C197" t="s">
+        <v>233</v>
+      </c>
+      <c r="D197">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>35</v>
+      </c>
+      <c r="B198" t="s">
+        <v>206</v>
+      </c>
+      <c r="C198" t="s">
+        <v>234</v>
+      </c>
+      <c r="D198">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>35</v>
+      </c>
+      <c r="B199" t="s">
+        <v>201</v>
+      </c>
+      <c r="C199" t="s">
+        <v>235</v>
+      </c>
+      <c r="D199">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>35</v>
+      </c>
+      <c r="B200" t="s">
+        <v>185</v>
+      </c>
+      <c r="C200" t="s">
+        <v>236</v>
+      </c>
+      <c r="D200">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>35</v>
+      </c>
+      <c r="B201" t="s">
+        <v>185</v>
+      </c>
+      <c r="C201" t="s">
+        <v>237</v>
+      </c>
+      <c r="D201">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>69</v>
+      </c>
+      <c r="B202" t="s">
+        <v>238</v>
+      </c>
+      <c r="C202" t="s">
+        <v>239</v>
+      </c>
+      <c r="D202">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>69</v>
+      </c>
+      <c r="B203" t="s">
+        <v>238</v>
+      </c>
+      <c r="C203" t="s">
+        <v>240</v>
+      </c>
+      <c r="D203">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>69</v>
+      </c>
+      <c r="B204" t="s">
+        <v>238</v>
+      </c>
+      <c r="C204" t="s">
+        <v>241</v>
+      </c>
+      <c r="D204">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>69</v>
+      </c>
+      <c r="B205" t="s">
+        <v>238</v>
+      </c>
+      <c r="C205" t="s">
+        <v>242</v>
+      </c>
+      <c r="D205">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>69</v>
+      </c>
+      <c r="B206" t="s">
+        <v>238</v>
+      </c>
+      <c r="C206" t="s">
+        <v>243</v>
+      </c>
+      <c r="D206">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>69</v>
+      </c>
+      <c r="B207" t="s">
+        <v>238</v>
+      </c>
+      <c r="C207" t="s">
+        <v>244</v>
+      </c>
+      <c r="D207">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>69</v>
+      </c>
+      <c r="B208" t="s">
+        <v>238</v>
+      </c>
+      <c r="C208" t="s">
+        <v>245</v>
+      </c>
+      <c r="D208">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
+        <v>69</v>
+      </c>
+      <c r="B209" t="s">
+        <v>238</v>
+      </c>
+      <c r="C209" t="s">
+        <v>246</v>
+      </c>
+      <c r="D209">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
+        <v>69</v>
+      </c>
+      <c r="B210" t="s">
+        <v>238</v>
+      </c>
+      <c r="C210" t="s">
+        <v>247</v>
+      </c>
+      <c r="D210">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>69</v>
+      </c>
+      <c r="B211" t="s">
+        <v>238</v>
+      </c>
+      <c r="C211" t="s">
+        <v>248</v>
+      </c>
+      <c r="D211">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>69</v>
+      </c>
+      <c r="B212" t="s">
+        <v>238</v>
+      </c>
+      <c r="C212" t="s">
+        <v>249</v>
+      </c>
+      <c r="D212">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>69</v>
+      </c>
+      <c r="B213" t="s">
+        <v>238</v>
+      </c>
+      <c r="C213" t="s">
+        <v>250</v>
+      </c>
+      <c r="D213">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>69</v>
+      </c>
+      <c r="B214" t="s">
+        <v>238</v>
+      </c>
+      <c r="C214" t="s">
+        <v>251</v>
+      </c>
+      <c r="D214">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>69</v>
+      </c>
+      <c r="B215" t="s">
+        <v>75</v>
+      </c>
+      <c r="C215" t="s">
+        <v>252</v>
+      </c>
+      <c r="D215">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>69</v>
+      </c>
+      <c r="B216" t="s">
+        <v>75</v>
+      </c>
+      <c r="C216" t="s">
+        <v>253</v>
+      </c>
+      <c r="D216">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>69</v>
+      </c>
+      <c r="B217" t="s">
+        <v>75</v>
+      </c>
+      <c r="C217" t="s">
+        <v>254</v>
+      </c>
+      <c r="D217">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>69</v>
+      </c>
+      <c r="B218" t="s">
+        <v>75</v>
+      </c>
+      <c r="C218" t="s">
+        <v>255</v>
+      </c>
+      <c r="D218">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>69</v>
+      </c>
+      <c r="B219" t="s">
+        <v>75</v>
+      </c>
+      <c r="C219" t="s">
+        <v>256</v>
+      </c>
+      <c r="D219">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>69</v>
+      </c>
+      <c r="B220" t="s">
+        <v>75</v>
+      </c>
+      <c r="C220" t="s">
+        <v>257</v>
+      </c>
+      <c r="D220">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>69</v>
+      </c>
+      <c r="B221" t="s">
+        <v>75</v>
+      </c>
+      <c r="C221" t="s">
+        <v>258</v>
+      </c>
+      <c r="D221">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>69</v>
+      </c>
+      <c r="B222" t="s">
+        <v>75</v>
+      </c>
+      <c r="C222" t="s">
+        <v>259</v>
+      </c>
+      <c r="D222">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>69</v>
+      </c>
+      <c r="B223" t="s">
+        <v>75</v>
+      </c>
+      <c r="C223" t="s">
+        <v>260</v>
+      </c>
+      <c r="D223">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>69</v>
+      </c>
+      <c r="B224" t="s">
+        <v>75</v>
+      </c>
+      <c r="C224" t="s">
+        <v>261</v>
+      </c>
+      <c r="D224">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>69</v>
+      </c>
+      <c r="B225" t="s">
+        <v>75</v>
+      </c>
+      <c r="C225" t="s">
+        <v>81</v>
+      </c>
+      <c r="D225">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>69</v>
+      </c>
+      <c r="B226" t="s">
+        <v>75</v>
+      </c>
+      <c r="C226" t="s">
+        <v>82</v>
+      </c>
+      <c r="D226">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>69</v>
+      </c>
+      <c r="B227" t="s">
+        <v>75</v>
+      </c>
+      <c r="C227" t="s">
+        <v>262</v>
+      </c>
+      <c r="D227">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>69</v>
+      </c>
+      <c r="B228" t="s">
+        <v>75</v>
+      </c>
+      <c r="C228" t="s">
+        <v>263</v>
+      </c>
+      <c r="D228">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>69</v>
+      </c>
+      <c r="B229" t="s">
+        <v>75</v>
+      </c>
+      <c r="C229" t="s">
+        <v>264</v>
+      </c>
+      <c r="D229">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>69</v>
+      </c>
+      <c r="B230" t="s">
+        <v>75</v>
+      </c>
+      <c r="C230" t="s">
+        <v>265</v>
+      </c>
+      <c r="D230">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>69</v>
+      </c>
+      <c r="B231" t="s">
+        <v>75</v>
+      </c>
+      <c r="C231" t="s">
+        <v>266</v>
+      </c>
+      <c r="D231">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>69</v>
+      </c>
+      <c r="B232" t="s">
+        <v>75</v>
+      </c>
+      <c r="C232" t="s">
+        <v>267</v>
+      </c>
+      <c r="D232">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>69</v>
+      </c>
+      <c r="B233" t="s">
+        <v>75</v>
+      </c>
+      <c r="C233" t="s">
+        <v>268</v>
+      </c>
+      <c r="D233">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>69</v>
+      </c>
+      <c r="B234" t="s">
+        <v>269</v>
+      </c>
+      <c r="C234" t="s">
+        <v>270</v>
+      </c>
+      <c r="D234">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>69</v>
+      </c>
+      <c r="B235" t="s">
+        <v>269</v>
+      </c>
+      <c r="C235" t="s">
+        <v>271</v>
+      </c>
+      <c r="D235">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>69</v>
+      </c>
+      <c r="B236" t="s">
+        <v>269</v>
+      </c>
+      <c r="C236" t="s">
+        <v>272</v>
+      </c>
+      <c r="D236">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
+        <v>69</v>
+      </c>
+      <c r="B237" t="s">
+        <v>269</v>
+      </c>
+      <c r="C237" t="s">
+        <v>273</v>
+      </c>
+      <c r="D237">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>69</v>
+      </c>
+      <c r="B238" t="s">
+        <v>269</v>
+      </c>
+      <c r="C238" t="s">
+        <v>274</v>
+      </c>
+      <c r="D238">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>69</v>
+      </c>
+      <c r="B239" t="s">
+        <v>269</v>
+      </c>
+      <c r="C239" t="s">
+        <v>275</v>
+      </c>
+      <c r="D239">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>69</v>
+      </c>
+      <c r="B240" t="s">
+        <v>269</v>
+      </c>
+      <c r="C240" t="s">
+        <v>276</v>
+      </c>
+      <c r="D240">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A241" t="s">
+        <v>69</v>
+      </c>
+      <c r="B241" t="s">
+        <v>269</v>
+      </c>
+      <c r="C241" t="s">
+        <v>277</v>
+      </c>
+      <c r="D241">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>69</v>
+      </c>
+      <c r="B242" t="s">
+        <v>269</v>
+      </c>
+      <c r="C242" t="s">
+        <v>278</v>
+      </c>
+      <c r="D242">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>69</v>
+      </c>
+      <c r="B243" t="s">
+        <v>269</v>
+      </c>
+      <c r="C243" t="s">
+        <v>279</v>
+      </c>
+      <c r="D243">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A244" t="s">
+        <v>69</v>
+      </c>
+      <c r="B244" t="s">
+        <v>269</v>
+      </c>
+      <c r="C244" t="s">
+        <v>280</v>
+      </c>
+      <c r="D244">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A245" t="s">
+        <v>69</v>
+      </c>
+      <c r="B245" t="s">
+        <v>269</v>
+      </c>
+      <c r="C245" t="s">
+        <v>281</v>
+      </c>
+      <c r="D245">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A246" t="s">
+        <v>69</v>
+      </c>
+      <c r="B246" t="s">
+        <v>75</v>
+      </c>
+      <c r="C246" t="s">
+        <v>91</v>
+      </c>
+      <c r="D246">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>69</v>
+      </c>
+      <c r="B247" t="s">
+        <v>75</v>
+      </c>
+      <c r="C247" t="s">
+        <v>282</v>
+      </c>
+      <c r="D247">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>69</v>
+      </c>
+      <c r="B248" t="s">
+        <v>75</v>
+      </c>
+      <c r="C248" t="s">
+        <v>283</v>
+      </c>
+      <c r="D248">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>69</v>
+      </c>
+      <c r="B249" t="s">
+        <v>75</v>
+      </c>
+      <c r="C249" t="s">
+        <v>284</v>
+      </c>
+      <c r="D249">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A250" t="s">
+        <v>69</v>
+      </c>
+      <c r="B250" t="s">
+        <v>75</v>
+      </c>
+      <c r="C250" t="s">
+        <v>285</v>
+      </c>
+      <c r="D250">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
